--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.29698904784008</v>
+        <v>8.498260720274013</v>
       </c>
       <c r="D2" t="n">
-        <v>50.64203222343022</v>
+        <v>8.229330236307412</v>
       </c>
       <c r="E2" t="n">
-        <v>18.19330971077005</v>
+        <v>2.956412828000134</v>
       </c>
       <c r="F2" t="n">
-        <v>15.97804073916122</v>
+        <v>2.596431620113699</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.26216380441789</v>
+        <v>5.892601618217907</v>
       </c>
       <c r="D3" t="n">
-        <v>34.89808706634455</v>
+        <v>5.67093914828099</v>
       </c>
       <c r="E3" t="n">
-        <v>18.19330971077005</v>
+        <v>2.956412828000134</v>
       </c>
       <c r="F3" t="n">
-        <v>15.97804073916122</v>
+        <v>2.596431620113699</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.34126210720834</v>
+        <v>3.305455092421355</v>
       </c>
       <c r="D4" t="n">
-        <v>19.94155967995322</v>
+        <v>3.240503447992398</v>
       </c>
       <c r="E4" t="n">
-        <v>18.19330971077005</v>
+        <v>2.956412828000134</v>
       </c>
       <c r="F4" t="n">
-        <v>15.97804073916122</v>
+        <v>2.596431620113699</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49.52610261228056</v>
+        <v>8.047991674495591</v>
       </c>
       <c r="D5" t="n">
-        <v>46.71300272227008</v>
+        <v>7.590862942368889</v>
       </c>
       <c r="E5" t="n">
-        <v>18.19330971077005</v>
+        <v>2.956412828000134</v>
       </c>
       <c r="F5" t="n">
-        <v>15.97804073916122</v>
+        <v>2.596431620113699</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.81705660366666</v>
+        <v>6.957771698095833</v>
       </c>
       <c r="D6" t="n">
-        <v>45.69914423486851</v>
+        <v>7.426110938166134</v>
       </c>
       <c r="E6" t="n">
-        <v>18.19330971077005</v>
+        <v>2.956412828000134</v>
       </c>
       <c r="F6" t="n">
-        <v>15.97804073916122</v>
+        <v>2.596431620113699</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8.228401988634461</v>
+        <v>1.3371153231531</v>
       </c>
       <c r="D7" t="n">
-        <v>4.528210613258246</v>
+        <v>0.7358342246544651</v>
       </c>
       <c r="E7" t="n">
-        <v>18.19330971077005</v>
+        <v>2.956412828000134</v>
       </c>
       <c r="F7" t="n">
-        <v>15.97804073916122</v>
+        <v>2.596431620113699</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>4.267063142267774</v>
+        <v>0.6933977606185133</v>
       </c>
       <c r="D8" t="n">
-        <v>12.78124590615407</v>
+        <v>2.076952459750037</v>
       </c>
       <c r="E8" t="n">
-        <v>18.19330971077005</v>
+        <v>2.956412828000134</v>
       </c>
       <c r="F8" t="n">
-        <v>15.97804073916122</v>
+        <v>2.596431620113699</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.89712013774642</v>
+        <v>2.908282022383794</v>
       </c>
       <c r="D9" t="n">
-        <v>18.42881868228919</v>
+        <v>2.994683035871994</v>
       </c>
       <c r="E9" t="n">
-        <v>18.19330971077005</v>
+        <v>2.956412828000134</v>
       </c>
       <c r="F9" t="n">
-        <v>15.97804073916122</v>
+        <v>2.596431620113699</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.39954549088786</v>
+        <v>5.102426142269278</v>
       </c>
       <c r="D10" t="n">
-        <v>37.57778383711434</v>
+        <v>6.10638987353108</v>
       </c>
       <c r="E10" t="n">
-        <v>18.19330971077005</v>
+        <v>2.956412828000134</v>
       </c>
       <c r="F10" t="n">
-        <v>15.97804073916122</v>
+        <v>2.596431620113699</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>22.022210986898</v>
+        <v>3.578609285370926</v>
       </c>
       <c r="D11" t="n">
-        <v>29.81473723629581</v>
+        <v>4.84489480089807</v>
       </c>
       <c r="E11" t="n">
-        <v>18.19330971077005</v>
+        <v>2.956412828000134</v>
       </c>
       <c r="F11" t="n">
-        <v>15.97804073916122</v>
+        <v>2.596431620113699</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>17.81261419959786</v>
+        <v>2.894549807434652</v>
       </c>
       <c r="D12" t="n">
-        <v>22.9374497684254</v>
+        <v>3.727335587369128</v>
       </c>
       <c r="E12" t="n">
-        <v>18.19330971077005</v>
+        <v>2.956412828000134</v>
       </c>
       <c r="F12" t="n">
-        <v>15.97804073916122</v>
+        <v>2.596431620113699</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>29.72238672241366</v>
+        <v>4.82988784239222</v>
       </c>
       <c r="D13" t="n">
-        <v>33.77285965657507</v>
+        <v>5.48808969419345</v>
       </c>
       <c r="E13" t="n">
-        <v>18.19330971077005</v>
+        <v>2.956412828000134</v>
       </c>
       <c r="F13" t="n">
-        <v>15.97804073916122</v>
+        <v>2.596431620113699</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>29.85872477637587</v>
+        <v>4.852042776161078</v>
       </c>
       <c r="D14" t="n">
-        <v>30.54251180142506</v>
+        <v>4.963158167731573</v>
       </c>
       <c r="E14" t="n">
-        <v>18.19330971077005</v>
+        <v>2.956412828000134</v>
       </c>
       <c r="F14" t="n">
-        <v>15.97804073916122</v>
+        <v>2.596431620113699</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>56.85753101210676</v>
+        <v>9.23934878946735</v>
       </c>
       <c r="D15" t="n">
-        <v>32.86930115664301</v>
+        <v>5.34126143795449</v>
       </c>
       <c r="E15" t="n">
-        <v>18.19330971077005</v>
+        <v>2.956412828000134</v>
       </c>
       <c r="F15" t="n">
-        <v>15.97804073916122</v>
+        <v>2.596431620113699</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>55.7645602450474</v>
+        <v>9.061741039820202</v>
       </c>
       <c r="D16" t="n">
-        <v>56.18042915151185</v>
+        <v>9.129319737120676</v>
       </c>
       <c r="E16" t="n">
-        <v>18.19330971077005</v>
+        <v>2.956412828000134</v>
       </c>
       <c r="F16" t="n">
-        <v>15.97804073916122</v>
+        <v>2.596431620113699</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>68.63081504886051</v>
+        <v>11.15250744543983</v>
       </c>
       <c r="D17" t="n">
-        <v>67.04001738886309</v>
+        <v>10.89400282569025</v>
       </c>
       <c r="E17" t="n">
-        <v>18.19330971077005</v>
+        <v>2.956412828000134</v>
       </c>
       <c r="F17" t="n">
-        <v>15.97804073916122</v>
+        <v>2.596431620113699</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
